--- a/absa_data_cleaning/data/interim/buds_t1.1.xlsx
+++ b/absa_data_cleaning/data/interim/buds_t1.1.xlsx
@@ -29371,7 +29371,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>Tốt. Đeo dễ chịu. Chất lượng âm ở mức khá</t>
+          <t>ẩn danh</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -29387,7 +29387,8 @@
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr">
         <is>
-          <t>Được tặng kèm cân điện tử Huawei xịn xò luôn.
+          <t>Tốt. Đeo dễ chịu. Chất lượng âm ở mức khá
+Được tặng kèm cân điện tử Huawei xịn xò luôn.
 Nói chung là đáng tiền</t>
         </is>
       </c>
